--- a/artfynd/A 20947-2026 artfynd.xlsx
+++ b/artfynd/A 20947-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1180,60 +1180,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133882813</v>
+        <v>135259245</v>
       </c>
       <c r="B7" t="n">
-        <v>57162</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skärklitt, Dlr</t>
+          <t>Skärklitt S, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453595</v>
+        <v>453304</v>
       </c>
       <c r="R7" t="n">
-        <v>6795540</v>
+        <v>6795367</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1257,12 +1245,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1273,72 +1271,74 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133882866</v>
+        <v>135259247</v>
       </c>
       <c r="B8" t="n">
-        <v>58519</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102990</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skärklitt, Dlr</t>
+          <t>Skärklitt S, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453662</v>
+        <v>453365</v>
       </c>
       <c r="R8" t="n">
-        <v>6795583</v>
+        <v>6795447</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1362,12 +1362,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1378,26 +1388,36 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133882769</v>
+        <v>135259252</v>
       </c>
       <c r="B9" t="n">
-        <v>98060</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,41 +1425,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skärklitt, Klitten, Älvdalen, Dlr</t>
+          <t>Skärklitt S, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>453508</v>
+        <v>453330</v>
       </c>
       <c r="R9" t="n">
-        <v>6795509</v>
+        <v>6795363</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1463,12 +1484,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1477,29 +1508,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133882687</v>
+        <v>135260254</v>
       </c>
       <c r="B10" t="n">
-        <v>98063</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,41 +1537,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skärklitt, Klitten, Älvdalen, Dlr</t>
+          <t>Skärklitt S, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>453508</v>
+        <v>453655</v>
       </c>
       <c r="R10" t="n">
-        <v>6795509</v>
+        <v>6795376</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1565,12 +1596,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1579,22 +1620,1417 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135260257</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skärklitt S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>453668</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6795405</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135260259</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skärklitt S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>453670</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6795361</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133882813</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skärklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>453595</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6795540</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Gunnar Åhs</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Gunnar Åhs</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133882866</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58519</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skärklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>453662</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6795583</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135259246</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skärklitt S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>453333</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6795400</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135260249</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skärklitt S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>453665</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6795345</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135260256</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skärklitt S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>453653</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6795377</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135259248</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98066</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skärklitt S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>453271</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6795365</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133882769</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skärklitt, Klitten, Älvdalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>453508</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6795509</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135259249</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skärklitt S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>453268</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6795365</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135260251</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skärklitt S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>453648</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6795374</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133882687</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skärklitt, Klitten, Älvdalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>453508</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6795509</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135259251</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skärklitt S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>453288</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6795378</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20947-2026 artfynd.xlsx
+++ b/artfynd/A 20947-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133882562</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133882575</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133882591</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133882620</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133882840</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259245</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259247</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259252</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135260254</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135260257</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1859,6 +1914,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135260259</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1968,6 +2028,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133882813</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2073,6 +2138,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133882866</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2185,6 +2255,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259246</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2292,6 +2367,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135260249</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2399,6 +2479,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135260256</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2506,6 +2591,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259248</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2608,6 +2698,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133882769</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2715,6 +2810,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259249</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2822,6 +2922,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135260251</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2924,6 +3029,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133882687</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3031,8 +3141,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259251</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 20947-2026 artfynd.xlsx
+++ b/artfynd/A 20947-2026 artfynd.xlsx
@@ -1213,7 +1213,7 @@
         <v>135259245</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>135259247</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>135259252</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>135260254</v>
       </c>
       <c r="B10" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135260257</v>
       </c>
       <c r="B11" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135260259</v>
       </c>
       <c r="B12" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>135259246</v>
       </c>
       <c r="B15" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>135260249</v>
       </c>
       <c r="B16" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>135260256</v>
       </c>
       <c r="B17" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>135259248</v>
       </c>
       <c r="B18" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>135259249</v>
       </c>
       <c r="B20" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>135260251</v>
       </c>
       <c r="B21" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>135259251</v>
       </c>
       <c r="B23" t="n">
-        <v>98063</v>
+        <v>98107</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 20947-2026 artfynd.xlsx
+++ b/artfynd/A 20947-2026 artfynd.xlsx
@@ -1213,7 +1213,7 @@
         <v>135259245</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>135259247</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>135260249</v>
       </c>
       <c r="B16" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>135260256</v>
       </c>
       <c r="B17" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>135259248</v>
       </c>
       <c r="B18" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>135259249</v>
       </c>
       <c r="B20" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>135260251</v>
       </c>
       <c r="B21" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>135259251</v>
       </c>
       <c r="B23" t="n">
-        <v>98107</v>
+        <v>98134</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 20947-2026 artfynd.xlsx
+++ b/artfynd/A 20947-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1210,60 +1210,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133882813</v>
+        <v>135259245</v>
       </c>
       <c r="B7" t="n">
-        <v>57162</v>
+        <v>79441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skärklitt, Dlr</t>
+          <t>Skärklitt S, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453595</v>
+        <v>453304</v>
       </c>
       <c r="R7" t="n">
-        <v>6795540</v>
+        <v>6795367</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,12 +1275,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1303,77 +1301,79 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133882813</t>
+          <t>https://artportalen.se/Sighting/135259245</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133882866</v>
+        <v>135259247</v>
       </c>
       <c r="B8" t="n">
-        <v>58519</v>
+        <v>79441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102990</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skärklitt, Dlr</t>
+          <t>Skärklitt S, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453662</v>
+        <v>453365</v>
       </c>
       <c r="R8" t="n">
-        <v>6795583</v>
+        <v>6795447</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,12 +1397,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1413,31 +1423,41 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133882866</t>
+          <t>https://artportalen.se/Sighting/135259247</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133882769</v>
+        <v>135259252</v>
       </c>
       <c r="B9" t="n">
-        <v>98060</v>
+        <v>57977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,41 +1465,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skärklitt, Klitten, Älvdalen, Dlr</t>
+          <t>Skärklitt S, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>453508</v>
+        <v>453330</v>
       </c>
       <c r="R9" t="n">
-        <v>6795509</v>
+        <v>6795363</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1503,12 +1524,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1517,34 +1548,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133882769</t>
+          <t>https://artportalen.se/Sighting/135259252</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133882687</v>
+        <v>135260254</v>
       </c>
       <c r="B10" t="n">
-        <v>98063</v>
+        <v>57977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,41 +1582,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skärklitt, Klitten, Älvdalen, Dlr</t>
+          <t>Skärklitt S, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>453508</v>
+        <v>453655</v>
       </c>
       <c r="R10" t="n">
-        <v>6795509</v>
+        <v>6795376</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1610,12 +1641,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1624,25 +1665,1485 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135260254</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135260257</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skärklitt S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>453668</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6795405</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135260257</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135260259</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skärklitt S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>453670</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6795361</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135260259</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133882813</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skärklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>453595</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6795540</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133882813</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133882866</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58519</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skärklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>453662</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6795583</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133882866</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135259246</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skärklitt S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>453333</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6795400</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259246</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135260249</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skärklitt S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>453665</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6795345</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135260249</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135260256</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skärklitt S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>453653</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6795377</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135260256</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135259248</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98142</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skärklitt S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>453271</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6795365</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259248</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133882769</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skärklitt, Klitten, Älvdalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>453508</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6795509</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133882769</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135259249</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98136</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skärklitt S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>453268</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6795365</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259249</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135260251</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98136</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skärklitt S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>453648</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6795374</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135260251</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133882687</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skärklitt, Klitten, Älvdalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>453508</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6795509</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/133882687</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135259251</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98139</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skärklitt S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>453288</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6795378</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259251</t>
         </is>
       </c>
     </row>
@@ -1657,6 +3158,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20947-2026 artfynd.xlsx
+++ b/artfynd/A 20947-2026 artfynd.xlsx
@@ -2266,7 +2266,7 @@
         <v>135260249</v>
       </c>
       <c r="B16" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>135260256</v>
       </c>
       <c r="B17" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>135259248</v>
       </c>
       <c r="B18" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>135259249</v>
       </c>
       <c r="B20" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>135260251</v>
       </c>
       <c r="B21" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>135259251</v>
       </c>
       <c r="B23" t="n">
-        <v>98139</v>
+        <v>98141</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
